--- a/output/pdf_financials_xlsx/EPR.xlsx
+++ b/output/pdf_financials_xlsx/EPR.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.037641</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.107089</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.243028</v>
       </c>
     </row>
     <row r="93">
@@ -3082,7 +3082,11 @@
           <t>Warrants reserve 7</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.037641</v>
       </c>

--- a/output/pdf_financials_xlsx/EPR.xlsx
+++ b/output/pdf_financials_xlsx/EPR.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.026914</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003576</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001456</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.045302</v>
+        <v>-1.072216</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.188872</v>
+        <v>-1.192448</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.916424</v>
+        <v>-0.91788</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.045302</v>
+        <v>-1.072216</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.188872</v>
+        <v>-1.192448</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.916424</v>
+        <v>-0.91788</v>
       </c>
     </row>
     <row r="30">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">

--- a/output/pdf_financials_xlsx/EPR.xlsx
+++ b/output/pdf_financials_xlsx/EPR.xlsx
@@ -3640,7 +3640,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>1.307763</v>
       </c>
